--- a/pages/video_analysis/WTS_starts.xlsx
+++ b/pages/video_analysis/WTS_starts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4161D78B-EF18-4FF6-9702-3A3276E5B52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0943C42E-5478-4951-A802-8835630EDCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{BAE2881F-AFDF-458E-BC8D-8FE3C83F19F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="93">
   <si>
     <t>Name</t>
   </si>
@@ -283,6 +283,39 @@
   <si>
     <t>https://youtu.be/hB1yvgijXIY</t>
   </si>
+  <si>
+    <t>https://youtu.be/9kQ68w7E7T4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/cfdNOiZ-bV0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/04piwOYTzWw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SES0RMDM0ao</t>
+  </si>
+  <si>
+    <t>https://youtu.be/c3W3UkfReM8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ViXaoxzyxNQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-Hd7r1M98js</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ywh9RI0oNuE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fdIWsfIhjAU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vp7zdZOuf9M</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MOXj31sWarQ</t>
+  </si>
 </sst>
 </file>
 
@@ -291,7 +324,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,13 +340,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -325,10 +372,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -348,8 +396,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6953,7 +7006,7 @@
       </c>
       <c r="AM64" s="8"/>
     </row>
-    <row r="65" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>40</v>
       </c>
@@ -7046,7 +7099,7 @@
       </c>
       <c r="AM65" s="8"/>
     </row>
-    <row r="66" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>41</v>
       </c>
@@ -7139,7 +7192,7 @@
       </c>
       <c r="AM66" s="8"/>
     </row>
-    <row r="67" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>38</v>
       </c>
@@ -7235,7 +7288,7 @@
       </c>
       <c r="AM67" s="8"/>
     </row>
-    <row r="68" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>40</v>
       </c>
@@ -7331,7 +7384,7 @@
       </c>
       <c r="AM68" s="8"/>
     </row>
-    <row r="69" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>41</v>
       </c>
@@ -7427,7 +7480,7 @@
       </c>
       <c r="AM69" s="8"/>
     </row>
-    <row r="70" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>38</v>
       </c>
@@ -7523,7 +7576,7 @@
       </c>
       <c r="AM70" s="8"/>
     </row>
-    <row r="71" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>40</v>
       </c>
@@ -7619,7 +7672,7 @@
       </c>
       <c r="AM71" s="8"/>
     </row>
-    <row r="72" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>41</v>
       </c>
@@ -7715,7 +7768,7 @@
       </c>
       <c r="AM72" s="8"/>
     </row>
-    <row r="73" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>38</v>
       </c>
@@ -7817,7 +7870,7 @@
       </c>
       <c r="AN73" s="8"/>
     </row>
-    <row r="74" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -7919,7 +7972,7 @@
       </c>
       <c r="AN74" s="8"/>
     </row>
-    <row r="75" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>41</v>
       </c>
@@ -8015,7 +8068,7 @@
       </c>
       <c r="AM75" s="8"/>
     </row>
-    <row r="76" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>41</v>
       </c>
@@ -8140,7 +8193,7 @@
         <v>34.040000000000006</v>
       </c>
     </row>
-    <row r="77" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>38</v>
       </c>
@@ -8265,7 +8318,7 @@
         <v>34.36</v>
       </c>
     </row>
-    <row r="78" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -8390,23 +8443,23 @@
         <v>34.659999999999997</v>
       </c>
     </row>
-    <row r="79" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>41</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B79" s="9">
         <v>45089</v>
       </c>
-      <c r="C79" s="7">
-        <v>1</v>
-      </c>
-      <c r="D79" s="7">
-        <v>1</v>
-      </c>
-      <c r="E79">
-        <v>2</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="C79" s="10">
+        <v>1</v>
+      </c>
+      <c r="D79" s="10">
+        <v>1</v>
+      </c>
+      <c r="E79" s="11">
+        <v>2</v>
+      </c>
+      <c r="F79" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G79">
@@ -8480,24 +8533,27 @@
         <v>8.02</v>
       </c>
       <c r="AM79" s="8"/>
-    </row>
-    <row r="80" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="AP79" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>38</v>
       </c>
-      <c r="B80" s="6">
+      <c r="B80" s="9">
         <v>45089</v>
       </c>
-      <c r="C80" s="7">
-        <v>1</v>
-      </c>
-      <c r="D80" s="7">
-        <v>1</v>
-      </c>
-      <c r="E80">
+      <c r="C80" s="10">
+        <v>1</v>
+      </c>
+      <c r="D80" s="10">
+        <v>1</v>
+      </c>
+      <c r="E80" s="11">
         <v>3</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G80">
@@ -8569,24 +8625,27 @@
         <v>8.1800000000000033</v>
       </c>
       <c r="AM80" s="8"/>
-    </row>
-    <row r="81" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP80" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>40</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B81" s="9">
         <v>45089</v>
       </c>
-      <c r="C81" s="7">
-        <v>1</v>
-      </c>
-      <c r="D81" s="7">
-        <v>1</v>
-      </c>
-      <c r="E81">
+      <c r="C81" s="10">
+        <v>1</v>
+      </c>
+      <c r="D81" s="10">
+        <v>1</v>
+      </c>
+      <c r="E81" s="11">
         <v>3</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G81">
@@ -8658,24 +8717,27 @@
         <v>8.1900000000000013</v>
       </c>
       <c r="AM81" s="8"/>
-    </row>
-    <row r="82" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>40</v>
       </c>
-      <c r="B82" s="6">
+      <c r="B82" s="9">
         <v>45089</v>
       </c>
-      <c r="C82" s="7">
-        <v>1</v>
-      </c>
-      <c r="D82" s="7">
-        <v>2</v>
-      </c>
-      <c r="E82">
+      <c r="C82" s="10">
+        <v>1</v>
+      </c>
+      <c r="D82" s="10">
+        <v>2</v>
+      </c>
+      <c r="E82" s="11">
         <v>3</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G82">
@@ -8722,24 +8784,27 @@
         <v>8.2790000000000035</v>
       </c>
       <c r="AM82" s="8"/>
-    </row>
-    <row r="83" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP82" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>41</v>
       </c>
-      <c r="B83" s="6">
+      <c r="B83" s="9">
         <v>45089</v>
       </c>
-      <c r="C83" s="7">
-        <v>1</v>
-      </c>
-      <c r="D83" s="7">
-        <v>2</v>
-      </c>
-      <c r="E83">
-        <v>2</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="C83" s="10">
+        <v>1</v>
+      </c>
+      <c r="D83" s="10">
+        <v>2</v>
+      </c>
+      <c r="E83" s="11">
+        <v>2</v>
+      </c>
+      <c r="F83" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G83">
@@ -8806,24 +8871,27 @@
         <v>8.2199999999999989</v>
       </c>
       <c r="AM83" s="8"/>
-    </row>
-    <row r="84" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP83" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>38</v>
       </c>
-      <c r="B84" s="6">
+      <c r="B84" s="9">
         <v>45089</v>
       </c>
-      <c r="C84" s="7">
-        <v>1</v>
-      </c>
-      <c r="D84" s="7">
-        <v>2</v>
-      </c>
-      <c r="E84">
-        <v>2</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="C84" s="10">
+        <v>1</v>
+      </c>
+      <c r="D84" s="10">
+        <v>2</v>
+      </c>
+      <c r="E84" s="11">
+        <v>2</v>
+      </c>
+      <c r="F84" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G84">
@@ -8870,24 +8938,27 @@
         <v>7.9999999999999964</v>
       </c>
       <c r="AM84" s="8"/>
-    </row>
-    <row r="85" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>36</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B85" s="9">
         <v>45089</v>
       </c>
-      <c r="C85" s="7">
-        <v>1</v>
-      </c>
-      <c r="D85" s="7">
-        <v>2</v>
-      </c>
-      <c r="E85">
-        <v>1</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="C85" s="10">
+        <v>1</v>
+      </c>
+      <c r="D85" s="10">
+        <v>2</v>
+      </c>
+      <c r="E85" s="11">
+        <v>1</v>
+      </c>
+      <c r="F85" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G85">
@@ -8954,24 +9025,27 @@
         <v>7.490000000000002</v>
       </c>
       <c r="AM85" s="8"/>
-    </row>
-    <row r="86" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP85" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="86" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>36</v>
       </c>
-      <c r="B86" s="6">
+      <c r="B86" s="9">
         <v>45089</v>
       </c>
-      <c r="C86" s="7">
-        <v>1</v>
-      </c>
-      <c r="D86" s="7">
+      <c r="C86" s="10">
+        <v>1</v>
+      </c>
+      <c r="D86" s="10">
         <v>3</v>
       </c>
-      <c r="E86">
-        <v>1</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="E86" s="11">
+        <v>1</v>
+      </c>
+      <c r="F86" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G86">
@@ -9020,24 +9094,27 @@
       <c r="AM86" s="8">
         <v>11.679000000000002</v>
       </c>
-    </row>
-    <row r="87" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP86" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="87" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>41</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B87" s="9">
         <v>45089</v>
       </c>
-      <c r="C87" s="7">
-        <v>1</v>
-      </c>
-      <c r="D87" s="7">
+      <c r="C87" s="10">
+        <v>1</v>
+      </c>
+      <c r="D87" s="10">
         <v>3</v>
       </c>
-      <c r="E87">
-        <v>2</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="E87" s="11">
+        <v>2</v>
+      </c>
+      <c r="F87" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G87">
@@ -9089,24 +9166,27 @@
       <c r="AM87" s="8">
         <v>12.278999999999996</v>
       </c>
-    </row>
-    <row r="88" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP87" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>38</v>
       </c>
-      <c r="B88" s="6">
+      <c r="B88" s="9">
         <v>45089</v>
       </c>
-      <c r="C88" s="7">
-        <v>1</v>
-      </c>
-      <c r="D88" s="7">
+      <c r="C88" s="10">
+        <v>1</v>
+      </c>
+      <c r="D88" s="10">
         <v>3</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="11">
         <v>3</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G88">
@@ -9158,24 +9238,27 @@
       <c r="AM88" s="8">
         <v>12.499000000000002</v>
       </c>
-    </row>
-    <row r="89" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP88" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>40</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B89" s="9">
         <v>45089</v>
       </c>
-      <c r="C89" s="7">
-        <v>1</v>
-      </c>
-      <c r="D89" s="7">
+      <c r="C89" s="10">
+        <v>1</v>
+      </c>
+      <c r="D89" s="10">
         <v>3</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="11">
         <v>3</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G89">
@@ -9225,24 +9308,27 @@
         <v>7.9949999999999974</v>
       </c>
       <c r="AM89" s="8"/>
-    </row>
-    <row r="90" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP89" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>40</v>
       </c>
-      <c r="B90" s="6">
+      <c r="B90" s="9">
         <v>45089</v>
       </c>
-      <c r="C90" s="7">
-        <v>2</v>
-      </c>
-      <c r="D90" s="7">
-        <v>1</v>
-      </c>
-      <c r="E90">
+      <c r="C90" s="10">
+        <v>2</v>
+      </c>
+      <c r="D90" s="10">
+        <v>1</v>
+      </c>
+      <c r="E90" s="11">
         <v>3</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G90">
@@ -9289,24 +9375,27 @@
         <v>8.0750000000000028</v>
       </c>
       <c r="AM90" s="8"/>
-    </row>
-    <row r="91" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP90" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="91" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>36</v>
       </c>
-      <c r="B91" s="6">
+      <c r="B91" s="9">
         <v>45089</v>
       </c>
-      <c r="C91" s="7">
-        <v>2</v>
-      </c>
-      <c r="D91" s="7">
-        <v>1</v>
-      </c>
-      <c r="E91">
-        <v>1</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="C91" s="10">
+        <v>2</v>
+      </c>
+      <c r="D91" s="10">
+        <v>1</v>
+      </c>
+      <c r="E91" s="11">
+        <v>1</v>
+      </c>
+      <c r="F91" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G91">
@@ -9350,24 +9439,27 @@
         <v>7.8949999999999996</v>
       </c>
       <c r="AM91" s="8"/>
-    </row>
-    <row r="92" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>38</v>
       </c>
-      <c r="B92" s="6">
+      <c r="B92" s="9">
         <v>45089</v>
       </c>
-      <c r="C92" s="7">
-        <v>2</v>
-      </c>
-      <c r="D92" s="7">
-        <v>1</v>
-      </c>
-      <c r="E92">
-        <v>2</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="C92" s="10">
+        <v>2</v>
+      </c>
+      <c r="D92" s="10">
+        <v>1</v>
+      </c>
+      <c r="E92" s="11">
+        <v>2</v>
+      </c>
+      <c r="F92" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G92">
@@ -9414,24 +9506,27 @@
         <v>8.1750000000000007</v>
       </c>
       <c r="AM92" s="8"/>
-    </row>
-    <row r="93" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>41</v>
       </c>
-      <c r="B93" s="6">
+      <c r="B93" s="9">
         <v>45089</v>
       </c>
-      <c r="C93" s="7">
-        <v>2</v>
-      </c>
-      <c r="D93" s="7">
-        <v>1</v>
-      </c>
-      <c r="E93">
-        <v>2</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="C93" s="10">
+        <v>2</v>
+      </c>
+      <c r="D93" s="10">
+        <v>1</v>
+      </c>
+      <c r="E93" s="11">
+        <v>2</v>
+      </c>
+      <c r="F93" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G93">
@@ -9478,24 +9573,27 @@
         <v>8.0999999999999979</v>
       </c>
       <c r="AM93" s="8"/>
-    </row>
-    <row r="94" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP93" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="94" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>36</v>
       </c>
-      <c r="B94" s="6">
+      <c r="B94" s="9">
         <v>45089</v>
       </c>
-      <c r="C94" s="7">
-        <v>2</v>
-      </c>
-      <c r="D94" s="7">
-        <v>2</v>
-      </c>
-      <c r="E94">
-        <v>1</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="C94" s="10">
+        <v>2</v>
+      </c>
+      <c r="D94" s="10">
+        <v>2</v>
+      </c>
+      <c r="E94" s="11">
+        <v>1</v>
+      </c>
+      <c r="F94" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G94">
@@ -9539,24 +9637,27 @@
         <v>7.4799999999999898</v>
       </c>
       <c r="AM94" s="8"/>
-    </row>
-    <row r="95" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP94" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>41</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B95" s="9">
         <v>45089</v>
       </c>
-      <c r="C95" s="7">
-        <v>2</v>
-      </c>
-      <c r="D95" s="7">
-        <v>2</v>
-      </c>
-      <c r="E95">
-        <v>2</v>
-      </c>
-      <c r="F95" t="s">
+      <c r="C95" s="10">
+        <v>2</v>
+      </c>
+      <c r="D95" s="10">
+        <v>2</v>
+      </c>
+      <c r="E95" s="11">
+        <v>2</v>
+      </c>
+      <c r="F95" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G95">
@@ -9603,24 +9704,27 @@
         <v>8.0799999999999983</v>
       </c>
       <c r="AM95" s="8"/>
-    </row>
-    <row r="96" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AP95" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>38</v>
       </c>
-      <c r="B96" s="6">
+      <c r="B96" s="9">
         <v>45089</v>
       </c>
-      <c r="C96" s="7">
-        <v>2</v>
-      </c>
-      <c r="D96" s="7">
-        <v>2</v>
-      </c>
-      <c r="E96">
+      <c r="C96" s="10">
+        <v>2</v>
+      </c>
+      <c r="D96" s="10">
+        <v>2</v>
+      </c>
+      <c r="E96" s="11">
         <v>3</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G96">
@@ -9667,24 +9771,27 @@
         <v>8.220000000000006</v>
       </c>
       <c r="AM96" s="8"/>
+      <c r="AP96" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="97" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>40</v>
       </c>
-      <c r="B97" s="6">
+      <c r="B97" s="9">
         <v>45089</v>
       </c>
-      <c r="C97" s="7">
-        <v>2</v>
-      </c>
-      <c r="D97" s="7">
-        <v>2</v>
-      </c>
-      <c r="E97">
+      <c r="C97" s="10">
+        <v>2</v>
+      </c>
+      <c r="D97" s="10">
+        <v>2</v>
+      </c>
+      <c r="E97" s="11">
         <v>3</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G97">
@@ -9731,24 +9838,27 @@
         <v>8.1559999999999988</v>
       </c>
       <c r="AM97" s="8"/>
+      <c r="AP97" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="98" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>38</v>
       </c>
-      <c r="B98" s="6">
+      <c r="B98" s="9">
         <v>45089</v>
       </c>
-      <c r="C98" s="7">
-        <v>2</v>
-      </c>
-      <c r="D98" s="7">
+      <c r="C98" s="10">
+        <v>2</v>
+      </c>
+      <c r="D98" s="10">
         <v>3</v>
       </c>
-      <c r="E98">
-        <v>2</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="E98" s="11">
+        <v>2</v>
+      </c>
+      <c r="F98" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G98">
@@ -9800,24 +9910,27 @@
       <c r="AM98" s="8">
         <v>12.316000000000003</v>
       </c>
+      <c r="AP98" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="99" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>36</v>
       </c>
-      <c r="B99" s="6">
+      <c r="B99" s="9">
         <v>45089</v>
       </c>
-      <c r="C99" s="7">
-        <v>2</v>
-      </c>
-      <c r="D99" s="7">
+      <c r="C99" s="10">
+        <v>2</v>
+      </c>
+      <c r="D99" s="10">
         <v>3</v>
       </c>
-      <c r="E99">
-        <v>1</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="E99" s="11">
+        <v>1</v>
+      </c>
+      <c r="F99" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G99">
@@ -9866,24 +9979,27 @@
       <c r="AM99" s="8">
         <v>11.77</v>
       </c>
+      <c r="AP99" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="100" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>40</v>
       </c>
-      <c r="B100" s="6">
+      <c r="B100" s="9">
         <v>45089</v>
       </c>
-      <c r="C100" s="7">
-        <v>2</v>
-      </c>
-      <c r="D100" s="7">
+      <c r="C100" s="10">
+        <v>2</v>
+      </c>
+      <c r="D100" s="10">
         <v>3</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="11">
         <v>3</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G100">
@@ -9933,6 +10049,9 @@
         <v>8.0800000000000018</v>
       </c>
       <c r="AM100" s="8"/>
+      <c r="AP100" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="101" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
@@ -13357,6 +13476,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="AP89" r:id="rId1" xr:uid="{7F294435-01F3-4E95-B493-E058CDB2E220}"/>
+    <hyperlink ref="AP80" r:id="rId2" xr:uid="{CE025F3B-0D0A-4A77-BDB8-5492D21F700D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/video_analysis/WTS_starts.xlsx
+++ b/pages/video_analysis/WTS_starts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0943C42E-5478-4951-A802-8835630EDCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9231A4DF-B2EE-4B92-94A4-62000428DD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{BAE2881F-AFDF-458E-BC8D-8FE3C83F19F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="134">
   <si>
     <t>Name</t>
   </si>
@@ -316,6 +316,129 @@
   <si>
     <t>https://youtu.be/MOXj31sWarQ</t>
   </si>
+  <si>
+    <t>https://youtu.be/GhB3xzNDe3E</t>
+  </si>
+  <si>
+    <t>https://youtu.be/k9f3I6dnJGs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2hK5LxuxVmY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/p_DDzfxvk0E</t>
+  </si>
+  <si>
+    <t>https://youtu.be/PQ0DzETcDbQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/cqDAJ4dXnZ0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/of6FaWJoKeM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aw64ulxcb5Q</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FP7_kllyiCs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DUQPsmLzgZE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2bkS0pHEXOE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/AtpP0796cj8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_Z1QZ0hw3NE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-_GcwILVHeU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/8TzlIxO6PiQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/E8u5Ud770HE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/YbwU6yv_GY0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/RSIJSiE8rRA</t>
+  </si>
+  <si>
+    <t>https://youtu.be/RJrpfETx540</t>
+  </si>
+  <si>
+    <t>https://youtu.be/P5w7ppfdZs4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/dax6_B5Ckes</t>
+  </si>
+  <si>
+    <t>https://youtu.be/kaVyEB5wKUg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ooqQWhbgNkg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_Gx_ZoxyZ78</t>
+  </si>
+  <si>
+    <t>https://youtu.be/dVD99ByxmZ0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/xJa-qw1GJyE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/C4lsigoyuuY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WTnW0bms6tg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/wvUrKHmOdP0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UwASEF9hEW0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Nrs6MaFU0g0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fWpfjDWGdbM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Nq2_yndRTgU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IzpZmw-s8hE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UJbIQ_X3k94</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iBaKwhaHQx0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uJAwV8nonOw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IpFi5typVfc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1bV_-P_EZs4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qvJO--fxe_8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DQHGZ-a3Qqg</t>
+  </si>
 </sst>
 </file>
 
@@ -349,7 +472,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,6 +482,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -376,7 +505,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -400,6 +529,9 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -725,7 +857,7 @@
     <col min="5" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.21875" customWidth="1"/>
+    <col min="8" max="8" width="6.21875" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="9.21875" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="7.33203125" hidden="1" customWidth="1"/>
@@ -745,8 +877,7 @@
     <col min="37" max="37" width="5.5546875" hidden="1" customWidth="1"/>
     <col min="38" max="38" width="8.44140625" hidden="1" customWidth="1"/>
     <col min="39" max="39" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="9.109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
@@ -1386,25 +1517,25 @@
       <c r="AO6" s="8"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="14">
         <v>45070</v>
       </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="C7" s="15">
+        <v>1</v>
+      </c>
+      <c r="D7" s="15">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="13">
         <v>62.5</v>
       </c>
       <c r="H7">
@@ -1482,25 +1613,25 @@
       <c r="AM7" s="8"/>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="14">
         <v>45070</v>
       </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="C8" s="15">
+        <v>1</v>
+      </c>
+      <c r="D8" s="15">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13">
+        <v>2</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="13">
         <v>62.5</v>
       </c>
       <c r="H8">
@@ -1578,25 +1709,25 @@
       <c r="AM8" s="8"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="14">
         <v>45070</v>
       </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1</v>
-      </c>
-      <c r="E9">
+      <c r="C9" s="15">
+        <v>1</v>
+      </c>
+      <c r="D9" s="15">
+        <v>1</v>
+      </c>
+      <c r="E9" s="13">
         <v>3</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="13">
         <v>62.5</v>
       </c>
       <c r="H9">
@@ -1674,25 +1805,25 @@
       <c r="AM9" s="8"/>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="14">
         <v>45070</v>
       </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="C10" s="15">
+        <v>1</v>
+      </c>
+      <c r="D10" s="15">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13">
+        <v>2</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="13">
         <v>62.5</v>
       </c>
       <c r="H10">
@@ -1770,25 +1901,25 @@
       <c r="AM10" s="8"/>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="14">
         <v>45070</v>
       </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="7">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="C11" s="15">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15">
+        <v>2</v>
+      </c>
+      <c r="E11" s="13">
+        <v>1</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="13">
         <v>62.5</v>
       </c>
       <c r="H11">
@@ -1866,25 +1997,25 @@
       <c r="AM11" s="8"/>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="14">
         <v>45070</v>
       </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="C12" s="15">
+        <v>1</v>
+      </c>
+      <c r="D12" s="15">
+        <v>2</v>
+      </c>
+      <c r="E12" s="13">
+        <v>2</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="13">
         <v>62.5</v>
       </c>
       <c r="H12">
@@ -1962,25 +2093,25 @@
       <c r="AM12" s="8"/>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="14">
         <v>45070</v>
       </c>
-      <c r="C13" s="7">
-        <v>1</v>
-      </c>
-      <c r="D13" s="7">
-        <v>2</v>
-      </c>
-      <c r="E13">
+      <c r="C13" s="15">
+        <v>1</v>
+      </c>
+      <c r="D13" s="15">
+        <v>2</v>
+      </c>
+      <c r="E13" s="13">
         <v>3</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="13">
         <v>62.5</v>
       </c>
       <c r="H13">
@@ -2058,25 +2189,25 @@
       <c r="AM13" s="8"/>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="14">
         <v>45070</v>
       </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="C14" s="15">
+        <v>1</v>
+      </c>
+      <c r="D14" s="15">
+        <v>2</v>
+      </c>
+      <c r="E14" s="13">
+        <v>2</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="13">
         <v>62.5</v>
       </c>
       <c r="H14">
@@ -2154,25 +2285,25 @@
       <c r="AM14" s="8"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="14">
         <v>45070</v>
       </c>
-      <c r="C15" s="7">
-        <v>1</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
         <v>3</v>
       </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E15" s="13">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="13">
         <v>125</v>
       </c>
       <c r="H15">
@@ -2255,25 +2386,25 @@
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="14">
         <v>45070</v>
       </c>
-      <c r="C16" s="7">
-        <v>1</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="C16" s="15">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
         <v>3</v>
       </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="13">
+        <v>2</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="13">
         <v>125</v>
       </c>
       <c r="H16">
@@ -2355,26 +2486,26 @@
         <v>12.21</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="14">
         <v>45070</v>
       </c>
-      <c r="C17" s="7">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7">
+      <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15">
         <v>3</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="13">
         <v>3</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="13">
         <v>125</v>
       </c>
       <c r="H17">
@@ -2456,26 +2587,26 @@
         <v>12.52</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="14">
         <v>45070</v>
       </c>
-      <c r="C18" s="7">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7">
+      <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="13">
+        <v>2</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="13">
         <v>125</v>
       </c>
       <c r="H18">
@@ -2557,26 +2688,26 @@
         <v>12.38</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="14">
         <v>45070</v>
       </c>
-      <c r="C19" s="7">
-        <v>2</v>
-      </c>
-      <c r="D19" s="7">
-        <v>1</v>
-      </c>
-      <c r="E19">
+      <c r="C19" s="15">
+        <v>2</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="13">
         <v>3</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="13">
         <v>62.5</v>
       </c>
       <c r="H19">
@@ -2653,26 +2784,26 @@
       </c>
       <c r="AM19" s="8"/>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="14">
         <v>45070</v>
       </c>
-      <c r="C20" s="7">
-        <v>2</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="C20" s="15">
+        <v>2</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13">
+        <v>2</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="13">
         <v>62.5</v>
       </c>
       <c r="H20">
@@ -2749,26 +2880,26 @@
       </c>
       <c r="AM20" s="8"/>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="14">
         <v>45070</v>
       </c>
-      <c r="C21" s="7">
-        <v>2</v>
-      </c>
-      <c r="D21" s="7">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="C21" s="15">
+        <v>2</v>
+      </c>
+      <c r="D21" s="15">
+        <v>1</v>
+      </c>
+      <c r="E21" s="13">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="13">
         <v>62.5</v>
       </c>
       <c r="H21">
@@ -2845,26 +2976,26 @@
       </c>
       <c r="AM21" s="8"/>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="14">
         <v>45070</v>
       </c>
-      <c r="C22" s="7">
-        <v>2</v>
-      </c>
-      <c r="D22" s="7">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="C22" s="15">
+        <v>2</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="13">
+        <v>2</v>
+      </c>
+      <c r="F22" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="13">
         <v>62.5</v>
       </c>
       <c r="H22">
@@ -2940,27 +3071,30 @@
         <v>8.0499999999999989</v>
       </c>
       <c r="AM22" s="8"/>
-    </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="AP22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="14">
         <v>45070</v>
       </c>
-      <c r="C23" s="7">
-        <v>2</v>
-      </c>
-      <c r="D23" s="7">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="C23" s="15">
+        <v>2</v>
+      </c>
+      <c r="D23" s="15">
+        <v>2</v>
+      </c>
+      <c r="E23" s="13">
+        <v>1</v>
+      </c>
+      <c r="F23" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="13">
         <v>62.5</v>
       </c>
       <c r="H23">
@@ -3036,27 +3170,30 @@
         <v>7.47</v>
       </c>
       <c r="AM23" s="8"/>
-    </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="AP23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="14">
         <v>45070</v>
       </c>
-      <c r="C24" s="7">
-        <v>2</v>
-      </c>
-      <c r="D24" s="7">
-        <v>2</v>
-      </c>
-      <c r="E24">
+      <c r="C24" s="15">
+        <v>2</v>
+      </c>
+      <c r="D24" s="15">
+        <v>2</v>
+      </c>
+      <c r="E24" s="13">
         <v>3</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="13">
         <v>62.5</v>
       </c>
       <c r="H24">
@@ -3132,27 +3269,30 @@
         <v>8.2800000000000011</v>
       </c>
       <c r="AM24" s="8"/>
-    </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="AP24" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="14">
         <v>45070</v>
       </c>
-      <c r="C25" s="7">
-        <v>2</v>
-      </c>
-      <c r="D25" s="7">
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="C25" s="15">
+        <v>2</v>
+      </c>
+      <c r="D25" s="15">
+        <v>2</v>
+      </c>
+      <c r="E25" s="13">
+        <v>2</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="13">
         <v>62.5</v>
       </c>
       <c r="H25">
@@ -3228,27 +3368,30 @@
         <v>7.9499999999999993</v>
       </c>
       <c r="AM25" s="8"/>
-    </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="AP25" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="14">
         <v>45070</v>
       </c>
-      <c r="C26" s="7">
-        <v>2</v>
-      </c>
-      <c r="D26" s="7">
-        <v>2</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="C26" s="15">
+        <v>2</v>
+      </c>
+      <c r="D26" s="15">
+        <v>2</v>
+      </c>
+      <c r="E26" s="13">
+        <v>2</v>
+      </c>
+      <c r="F26" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="13">
         <v>62.5</v>
       </c>
       <c r="H26">
@@ -3324,27 +3467,30 @@
         <v>8.0300000000000011</v>
       </c>
       <c r="AM26" s="8"/>
-    </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="AP26" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="14">
         <v>45070</v>
       </c>
-      <c r="C27" s="7">
-        <v>2</v>
-      </c>
-      <c r="D27" s="7">
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="D27" s="15">
         <v>3</v>
       </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E27" s="13">
+        <v>1</v>
+      </c>
+      <c r="F27" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="13">
         <v>125</v>
       </c>
       <c r="H27">
@@ -3425,27 +3571,30 @@
       <c r="AM27" s="8">
         <v>11.7</v>
       </c>
-    </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="AP27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="14">
         <v>45070</v>
       </c>
-      <c r="C28" s="7">
-        <v>2</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
         <v>3</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="13">
         <v>3</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="13">
         <v>125</v>
       </c>
       <c r="H28">
@@ -3526,27 +3675,30 @@
       <c r="AM28" s="8">
         <v>12.450000000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="AP28" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="14">
         <v>45070</v>
       </c>
-      <c r="C29" s="7">
-        <v>2</v>
-      </c>
-      <c r="D29" s="7">
+      <c r="C29" s="15">
+        <v>2</v>
+      </c>
+      <c r="D29" s="15">
         <v>3</v>
       </c>
-      <c r="E29">
-        <v>2</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E29" s="13">
+        <v>2</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="13">
         <v>125</v>
       </c>
       <c r="H29">
@@ -3627,27 +3779,30 @@
       <c r="AM29" s="8">
         <v>12.34</v>
       </c>
-    </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="AP29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="14">
         <v>45070</v>
       </c>
-      <c r="C30" s="7">
-        <v>2</v>
-      </c>
-      <c r="D30" s="7">
+      <c r="C30" s="15">
+        <v>2</v>
+      </c>
+      <c r="D30" s="15">
         <v>3</v>
       </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" s="13">
+        <v>2</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="13">
         <v>125</v>
       </c>
       <c r="H30">
@@ -3728,27 +3883,30 @@
       <c r="AM30" s="8">
         <v>12.301000000000002</v>
       </c>
-    </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="AP30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="14">
         <v>45070</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="15">
         <v>3</v>
       </c>
-      <c r="D31" s="7">
-        <v>1</v>
-      </c>
-      <c r="E31">
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="13">
         <v>3</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="13">
         <v>62.5</v>
       </c>
       <c r="H31">
@@ -3825,26 +3983,26 @@
       </c>
       <c r="AM31" s="8"/>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="14">
         <v>45070</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="15">
         <v>3</v>
       </c>
-      <c r="D32" s="7">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>2</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="D32" s="15">
+        <v>1</v>
+      </c>
+      <c r="E32" s="13">
+        <v>2</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="13">
         <v>62.5</v>
       </c>
       <c r="H32">
@@ -3922,26 +4080,26 @@
       <c r="AM32" s="8"/>
       <c r="AO32" s="8"/>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="14">
         <v>45070</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="15">
         <v>3</v>
       </c>
-      <c r="D33" s="7">
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13">
+        <v>1</v>
+      </c>
+      <c r="F33" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="13">
         <v>62.5</v>
       </c>
       <c r="H33">
@@ -4018,26 +4176,26 @@
       </c>
       <c r="AM33" s="8"/>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="14">
         <v>45070</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="15">
         <v>3</v>
       </c>
-      <c r="D34" s="7">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>2</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="D34" s="15">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13">
+        <v>2</v>
+      </c>
+      <c r="F34" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="13">
         <v>62.5</v>
       </c>
       <c r="H34">
@@ -4113,27 +4271,30 @@
         <v>8</v>
       </c>
       <c r="AM34" s="8"/>
-    </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="AP34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="14">
         <v>45070</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="15">
         <v>3</v>
       </c>
-      <c r="D35" s="7">
-        <v>2</v>
-      </c>
-      <c r="E35">
+      <c r="D35" s="15">
+        <v>2</v>
+      </c>
+      <c r="E35" s="13">
         <v>3</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="13">
         <v>62.5</v>
       </c>
       <c r="H35">
@@ -4210,26 +4371,26 @@
       </c>
       <c r="AM35" s="8"/>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="14">
         <v>45070</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="15">
         <v>3</v>
       </c>
-      <c r="D36" s="7">
-        <v>2</v>
-      </c>
-      <c r="E36">
-        <v>2</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="D36" s="15">
+        <v>2</v>
+      </c>
+      <c r="E36" s="13">
+        <v>2</v>
+      </c>
+      <c r="F36" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="13">
         <v>62.5</v>
       </c>
       <c r="H36">
@@ -4307,26 +4468,26 @@
       <c r="AM36" s="8"/>
       <c r="AO36" s="8"/>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="14">
         <v>45070</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="15">
         <v>3</v>
       </c>
-      <c r="D37" s="7">
-        <v>2</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="D37" s="15">
+        <v>2</v>
+      </c>
+      <c r="E37" s="13">
+        <v>1</v>
+      </c>
+      <c r="F37" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="13">
         <v>62.5</v>
       </c>
       <c r="H37">
@@ -4403,26 +4564,26 @@
       </c>
       <c r="AM37" s="8"/>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="14">
         <v>45070</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="15">
         <v>3</v>
       </c>
-      <c r="D38" s="7">
-        <v>2</v>
-      </c>
-      <c r="E38">
-        <v>2</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="D38" s="15">
+        <v>2</v>
+      </c>
+      <c r="E38" s="13">
+        <v>2</v>
+      </c>
+      <c r="F38" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="13">
         <v>62.5</v>
       </c>
       <c r="H38">
@@ -4498,27 +4659,30 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="AM38" s="8"/>
-    </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="AP38" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="14">
         <v>45070</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="15">
         <v>3</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="15">
         <v>3</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="13">
         <v>3</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="13">
         <v>125</v>
       </c>
       <c r="H39">
@@ -4600,26 +4764,26 @@
         <v>12.469999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="6">
+      <c r="B40" s="14">
         <v>45070</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="15">
         <v>3</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="15">
         <v>3</v>
       </c>
-      <c r="E40">
-        <v>2</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E40" s="13">
+        <v>2</v>
+      </c>
+      <c r="F40" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="13">
         <v>125</v>
       </c>
       <c r="H40">
@@ -4701,26 +4865,26 @@
         <v>12.280000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="14">
         <v>45070</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="15">
         <v>3</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="15">
         <v>3</v>
       </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E41" s="13">
+        <v>1</v>
+      </c>
+      <c r="F41" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="13">
         <v>125</v>
       </c>
       <c r="H41">
@@ -4802,26 +4966,26 @@
         <v>11.878</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="14">
         <v>45070</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="15">
         <v>3</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="15">
         <v>3</v>
       </c>
-      <c r="E42">
-        <v>2</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="E42" s="13">
+        <v>2</v>
+      </c>
+      <c r="F42" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="13">
         <v>125</v>
       </c>
       <c r="H42">
@@ -4902,24 +5066,27 @@
       <c r="AM42" s="8">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="AP42" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="9">
         <v>45079</v>
       </c>
-      <c r="C43" s="7">
-        <v>1</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1</v>
-      </c>
-      <c r="E43">
-        <v>2</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="C43" s="10">
+        <v>1</v>
+      </c>
+      <c r="D43" s="10">
+        <v>1</v>
+      </c>
+      <c r="E43" s="11">
+        <v>2</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G43">
@@ -4995,24 +5162,27 @@
         <v>7.9400000000000048</v>
       </c>
       <c r="AM43" s="8"/>
-    </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="AP43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="9">
         <v>45079</v>
       </c>
-      <c r="C44" s="7">
-        <v>1</v>
-      </c>
-      <c r="D44" s="7">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>2</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="C44" s="10">
+        <v>1</v>
+      </c>
+      <c r="D44" s="10">
+        <v>1</v>
+      </c>
+      <c r="E44" s="11">
+        <v>2</v>
+      </c>
+      <c r="F44" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G44">
@@ -5088,24 +5258,27 @@
         <v>7.9609999999999985</v>
       </c>
       <c r="AM44" s="8"/>
-    </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="AP44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="9">
         <v>45079</v>
       </c>
-      <c r="C45" s="7">
-        <v>1</v>
-      </c>
-      <c r="D45" s="7">
-        <v>1</v>
-      </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="C45" s="10">
+        <v>1</v>
+      </c>
+      <c r="D45" s="10">
+        <v>1</v>
+      </c>
+      <c r="E45" s="11">
+        <v>2</v>
+      </c>
+      <c r="F45" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G45">
@@ -5181,24 +5354,27 @@
         <v>8.0790000000000006</v>
       </c>
       <c r="AM45" s="8"/>
-    </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="AP45" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="9">
         <v>45079</v>
       </c>
-      <c r="C46" s="7">
-        <v>1</v>
-      </c>
-      <c r="D46" s="7">
-        <v>2</v>
-      </c>
-      <c r="E46">
-        <v>2</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="C46" s="10">
+        <v>1</v>
+      </c>
+      <c r="D46" s="10">
+        <v>2</v>
+      </c>
+      <c r="E46" s="11">
+        <v>2</v>
+      </c>
+      <c r="F46" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G46">
@@ -5274,24 +5450,27 @@
         <v>7.9190000000000005</v>
       </c>
       <c r="AM46" s="8"/>
-    </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="AP46" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="9">
         <v>45079</v>
       </c>
-      <c r="C47" s="7">
-        <v>1</v>
-      </c>
-      <c r="D47" s="7">
-        <v>2</v>
-      </c>
-      <c r="E47">
-        <v>2</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="C47" s="10">
+        <v>1</v>
+      </c>
+      <c r="D47" s="10">
+        <v>2</v>
+      </c>
+      <c r="E47" s="11">
+        <v>2</v>
+      </c>
+      <c r="F47" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G47">
@@ -5367,24 +5546,27 @@
         <v>7.9989999999999988</v>
       </c>
       <c r="AM47" s="8"/>
-    </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="AP47" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="9">
         <v>45079</v>
       </c>
-      <c r="C48" s="7">
-        <v>1</v>
-      </c>
-      <c r="D48" s="7">
-        <v>2</v>
-      </c>
-      <c r="E48">
-        <v>2</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="C48" s="10">
+        <v>1</v>
+      </c>
+      <c r="D48" s="10">
+        <v>2</v>
+      </c>
+      <c r="E48" s="11">
+        <v>2</v>
+      </c>
+      <c r="F48" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G48">
@@ -5460,24 +5642,27 @@
         <v>8.0889999999999986</v>
       </c>
       <c r="AM48" s="8"/>
-    </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="AP48" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="9">
         <v>45079</v>
       </c>
-      <c r="C49" s="7">
-        <v>1</v>
-      </c>
-      <c r="D49" s="7">
+      <c r="C49" s="10">
+        <v>1</v>
+      </c>
+      <c r="D49" s="10">
         <v>3</v>
       </c>
-      <c r="E49">
-        <v>2</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="E49" s="11">
+        <v>2</v>
+      </c>
+      <c r="F49" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G49">
@@ -5558,24 +5743,27 @@
       <c r="AM49" s="8">
         <v>12.32</v>
       </c>
-    </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="AP49" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="6">
+      <c r="B50" s="9">
         <v>45079</v>
       </c>
-      <c r="C50" s="7">
-        <v>1</v>
-      </c>
-      <c r="D50" s="7">
+      <c r="C50" s="10">
+        <v>1</v>
+      </c>
+      <c r="D50" s="10">
         <v>3</v>
       </c>
-      <c r="E50">
-        <v>2</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="E50" s="11">
+        <v>2</v>
+      </c>
+      <c r="F50" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G50">
@@ -5656,24 +5844,27 @@
       <c r="AM50" s="8">
         <v>12.399999999999999</v>
       </c>
-    </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="AP50" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="9">
         <v>45079</v>
       </c>
-      <c r="C51" s="7">
-        <v>1</v>
-      </c>
-      <c r="D51" s="7">
+      <c r="C51" s="10">
+        <v>1</v>
+      </c>
+      <c r="D51" s="10">
         <v>3</v>
       </c>
-      <c r="E51">
-        <v>2</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="E51" s="11">
+        <v>2</v>
+      </c>
+      <c r="F51" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G51">
@@ -5754,24 +5945,27 @@
       <c r="AM51" s="8">
         <v>12.500999999999998</v>
       </c>
-    </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="AP51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B52" s="6">
+      <c r="B52" s="9">
         <v>45079</v>
       </c>
-      <c r="C52" s="7">
-        <v>1</v>
-      </c>
-      <c r="D52" s="7">
+      <c r="C52" s="10">
+        <v>1</v>
+      </c>
+      <c r="D52" s="10">
         <v>4</v>
       </c>
-      <c r="E52">
-        <v>2</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="E52" s="11">
+        <v>2</v>
+      </c>
+      <c r="F52" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G52">
@@ -5847,24 +6041,27 @@
         <v>8</v>
       </c>
       <c r="AM52" s="8"/>
-    </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="AP52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="9">
         <v>45079</v>
       </c>
-      <c r="C53" s="7">
-        <v>1</v>
-      </c>
-      <c r="D53" s="7">
+      <c r="C53" s="10">
+        <v>1</v>
+      </c>
+      <c r="D53" s="10">
         <v>4</v>
       </c>
-      <c r="E53">
-        <v>2</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="E53" s="11">
+        <v>2</v>
+      </c>
+      <c r="F53" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G53">
@@ -5940,24 +6137,27 @@
         <v>8.0990000000000002</v>
       </c>
       <c r="AM53" s="8"/>
-    </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="AP53" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54" s="9">
         <v>45079</v>
       </c>
-      <c r="C54" s="7">
-        <v>1</v>
-      </c>
-      <c r="D54" s="7">
+      <c r="C54" s="10">
+        <v>1</v>
+      </c>
+      <c r="D54" s="10">
         <v>4</v>
       </c>
-      <c r="E54">
-        <v>2</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="E54" s="11">
+        <v>2</v>
+      </c>
+      <c r="F54" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G54">
@@ -6033,24 +6233,27 @@
         <v>8.1409999999999982</v>
       </c>
       <c r="AM54" s="8"/>
-    </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="AP54" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="9">
         <v>45079</v>
       </c>
-      <c r="C55" s="7">
-        <v>2</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1</v>
-      </c>
-      <c r="E55">
-        <v>2</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="C55" s="10">
+        <v>2</v>
+      </c>
+      <c r="D55" s="10">
+        <v>1</v>
+      </c>
+      <c r="E55" s="11">
+        <v>2</v>
+      </c>
+      <c r="F55" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G55">
@@ -6126,24 +6329,27 @@
         <v>7.8100000000000023</v>
       </c>
       <c r="AM55" s="8"/>
-    </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="AP55" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56" s="9">
         <v>45079</v>
       </c>
-      <c r="C56" s="7">
-        <v>2</v>
-      </c>
-      <c r="D56" s="7">
-        <v>1</v>
-      </c>
-      <c r="E56">
-        <v>2</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="C56" s="10">
+        <v>2</v>
+      </c>
+      <c r="D56" s="10">
+        <v>1</v>
+      </c>
+      <c r="E56" s="11">
+        <v>2</v>
+      </c>
+      <c r="F56" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G56">
@@ -6219,24 +6425,27 @@
         <v>8.0100000000000051</v>
       </c>
       <c r="AM56" s="8"/>
-    </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="AP56" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="9">
         <v>45079</v>
       </c>
-      <c r="C57" s="7">
-        <v>2</v>
-      </c>
-      <c r="D57" s="7">
-        <v>1</v>
-      </c>
-      <c r="E57">
-        <v>2</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="C57" s="10">
+        <v>2</v>
+      </c>
+      <c r="D57" s="10">
+        <v>1</v>
+      </c>
+      <c r="E57" s="11">
+        <v>2</v>
+      </c>
+      <c r="F57" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G57">
@@ -6312,24 +6521,27 @@
         <v>8.0799999999999983</v>
       </c>
       <c r="AM57" s="8"/>
-    </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="AP57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="9">
         <v>45079</v>
       </c>
-      <c r="C58" s="7">
-        <v>2</v>
-      </c>
-      <c r="D58" s="7">
-        <v>2</v>
-      </c>
-      <c r="E58">
-        <v>2</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="C58" s="10">
+        <v>2</v>
+      </c>
+      <c r="D58" s="10">
+        <v>2</v>
+      </c>
+      <c r="E58" s="11">
+        <v>2</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G58">
@@ -6419,24 +6631,27 @@
       <c r="AN58" s="8">
         <v>19.751000000000001</v>
       </c>
-    </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="AP58" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="9">
         <v>45079</v>
       </c>
-      <c r="C59" s="7">
-        <v>2</v>
-      </c>
-      <c r="D59" s="7">
-        <v>2</v>
-      </c>
-      <c r="E59">
-        <v>2</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="C59" s="10">
+        <v>2</v>
+      </c>
+      <c r="D59" s="10">
+        <v>2</v>
+      </c>
+      <c r="E59" s="11">
+        <v>2</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G59">
@@ -6526,24 +6741,27 @@
       <c r="AN59" s="8">
         <v>19.848999999999997</v>
       </c>
-    </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="AP59" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B60" s="9">
         <v>45079</v>
       </c>
-      <c r="C60" s="7">
-        <v>2</v>
-      </c>
-      <c r="D60" s="7">
-        <v>2</v>
-      </c>
-      <c r="E60">
-        <v>2</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="C60" s="10">
+        <v>2</v>
+      </c>
+      <c r="D60" s="10">
+        <v>2</v>
+      </c>
+      <c r="E60" s="11">
+        <v>2</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G60">
@@ -6633,24 +6851,27 @@
       <c r="AN60" s="8">
         <v>20.144999999999996</v>
       </c>
-    </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="AP60" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="9">
         <v>45079</v>
       </c>
-      <c r="C61" s="7">
-        <v>2</v>
-      </c>
-      <c r="D61" s="7">
+      <c r="C61" s="10">
+        <v>2</v>
+      </c>
+      <c r="D61" s="10">
         <v>3</v>
       </c>
-      <c r="E61">
-        <v>2</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="E61" s="11">
+        <v>2</v>
+      </c>
+      <c r="F61" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G61">
@@ -6726,24 +6947,27 @@
         <v>7.8800000000000026</v>
       </c>
       <c r="AM61" s="8"/>
-    </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="AP61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B62" s="9">
         <v>45079</v>
       </c>
-      <c r="C62" s="7">
-        <v>2</v>
-      </c>
-      <c r="D62" s="7">
+      <c r="C62" s="10">
+        <v>2</v>
+      </c>
+      <c r="D62" s="10">
         <v>3</v>
       </c>
-      <c r="E62">
-        <v>2</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="E62" s="11">
+        <v>2</v>
+      </c>
+      <c r="F62" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G62">
@@ -6819,24 +7043,27 @@
         <v>8.0600000000000023</v>
       </c>
       <c r="AM62" s="8"/>
-    </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="AP62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="9">
         <v>45079</v>
       </c>
-      <c r="C63" s="7">
-        <v>2</v>
-      </c>
-      <c r="D63" s="7">
+      <c r="C63" s="10">
+        <v>2</v>
+      </c>
+      <c r="D63" s="10">
         <v>3</v>
       </c>
-      <c r="E63">
-        <v>2</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="E63" s="11">
+        <v>2</v>
+      </c>
+      <c r="F63" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G63">
@@ -6912,24 +7139,27 @@
         <v>8.1810000000000009</v>
       </c>
       <c r="AM63" s="8"/>
-    </row>
-    <row r="64" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="AP63" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B64" s="6">
+      <c r="B64" s="9">
         <v>45079</v>
       </c>
-      <c r="C64" s="7">
-        <v>2</v>
-      </c>
-      <c r="D64" s="7">
+      <c r="C64" s="10">
+        <v>2</v>
+      </c>
+      <c r="D64" s="10">
         <v>4</v>
       </c>
-      <c r="E64">
-        <v>2</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="E64" s="11">
+        <v>2</v>
+      </c>
+      <c r="F64" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G64">
@@ -7005,24 +7235,27 @@
         <v>7.9399999999999977</v>
       </c>
       <c r="AM64" s="8"/>
+      <c r="AP64" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="65" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="9">
         <v>45079</v>
       </c>
-      <c r="C65" s="7">
-        <v>2</v>
-      </c>
-      <c r="D65" s="7">
+      <c r="C65" s="10">
+        <v>2</v>
+      </c>
+      <c r="D65" s="10">
         <v>4</v>
       </c>
-      <c r="E65">
-        <v>2</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="E65" s="11">
+        <v>2</v>
+      </c>
+      <c r="F65" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G65">
@@ -7098,24 +7331,27 @@
         <v>7.9999999999999982</v>
       </c>
       <c r="AM65" s="8"/>
+      <c r="AP65" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="66" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B66" s="9">
         <v>45079</v>
       </c>
-      <c r="C66" s="7">
-        <v>2</v>
-      </c>
-      <c r="D66" s="7">
+      <c r="C66" s="10">
+        <v>2</v>
+      </c>
+      <c r="D66" s="10">
         <v>4</v>
       </c>
-      <c r="E66">
-        <v>2</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="E66" s="11">
+        <v>2</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G66">
@@ -7191,6 +7427,9 @@
         <v>8.1809999999999974</v>
       </c>
       <c r="AM66" s="8"/>
+      <c r="AP66" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="67" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -7287,6 +7526,9 @@
         <v>7.9009999999999998</v>
       </c>
       <c r="AM67" s="8"/>
+      <c r="AP67" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="68" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -7383,6 +7625,9 @@
         <v>7.9799999999999986</v>
       </c>
       <c r="AM68" s="8"/>
+      <c r="AP68" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="69" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -7479,6 +7724,9 @@
         <v>7.91</v>
       </c>
       <c r="AM69" s="8"/>
+      <c r="AP69" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="70" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -7575,6 +7823,9 @@
         <v>7.92</v>
       </c>
       <c r="AM70" s="8"/>
+      <c r="AP70" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="71" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -7671,6 +7922,9 @@
         <v>7.9000000000000021</v>
       </c>
       <c r="AM71" s="8"/>
+      <c r="AP71" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="72" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -7767,6 +8021,9 @@
         <v>8.11</v>
       </c>
       <c r="AM72" s="8"/>
+      <c r="AP72" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="73" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -7869,6 +8126,9 @@
         <v>12.280000000000001</v>
       </c>
       <c r="AN73" s="8"/>
+      <c r="AP73" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="74" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -7971,6 +8231,9 @@
         <v>12.399000000000001</v>
       </c>
       <c r="AN74" s="8"/>
+      <c r="AP74" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="75" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -8067,6 +8330,9 @@
         <v>7.6700000000000017</v>
       </c>
       <c r="AM75" s="8"/>
+      <c r="AP75" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="76" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -8192,6 +8458,9 @@
       <c r="AO76" s="8">
         <v>34.040000000000006</v>
       </c>
+      <c r="AP76" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="77" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -8317,6 +8586,9 @@
       <c r="AO77" s="8">
         <v>34.36</v>
       </c>
+      <c r="AP77" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="78" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -8441,6 +8713,9 @@
       </c>
       <c r="AO78" s="8">
         <v>34.659999999999997</v>
+      </c>
+      <c r="AP78" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="79" spans="1:42" x14ac:dyDescent="0.3">
@@ -13479,6 +13754,7 @@
   <hyperlinks>
     <hyperlink ref="AP89" r:id="rId1" xr:uid="{7F294435-01F3-4E95-B493-E058CDB2E220}"/>
     <hyperlink ref="AP80" r:id="rId2" xr:uid="{CE025F3B-0D0A-4A77-BDB8-5492D21F700D}"/>
+    <hyperlink ref="AP54" r:id="rId3" xr:uid="{61E92077-7409-4F39-86D4-8C772F8E125A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/video_analysis/WTS_starts.xlsx
+++ b/pages/video_analysis/WTS_starts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9231A4DF-B2EE-4B92-94A4-62000428DD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E551164-63B0-42FE-8F7D-AB8D9B2E1E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{BAE2881F-AFDF-458E-BC8D-8FE3C83F19F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="144">
   <si>
     <t>Name</t>
   </si>
@@ -438,6 +438,36 @@
   </si>
   <si>
     <t>https://youtu.be/DQHGZ-a3Qqg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0yCqKIdssI0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aCXW8d0Usgo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_QgT5JH1HZc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jds-DV0YkLE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2G4uT9PneWk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/TBgSUgbeAjU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-LZPg7XKh-A</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2LFaez91oK0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/q4gDGEHOMp0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/HtHwScz6RgI</t>
   </si>
 </sst>
 </file>
@@ -1611,6 +1641,9 @@
         <v>7.34</v>
       </c>
       <c r="AM7" s="8"/>
+      <c r="AP7" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
@@ -1707,6 +1740,9 @@
         <v>7.9299999999999988</v>
       </c>
       <c r="AM8" s="8"/>
+      <c r="AP8" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
@@ -1803,6 +1839,9 @@
         <v>8.09</v>
       </c>
       <c r="AM9" s="8"/>
+      <c r="AP9" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
@@ -1899,6 +1938,9 @@
         <v>7.9700000000000006</v>
       </c>
       <c r="AM10" s="8"/>
+      <c r="AP10" s="12" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
@@ -1995,6 +2037,9 @@
         <v>7.36</v>
       </c>
       <c r="AM11" s="8"/>
+      <c r="AP11" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
@@ -2091,6 +2136,9 @@
         <v>7.89</v>
       </c>
       <c r="AM12" s="8"/>
+      <c r="AP12" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
@@ -2187,6 +2235,9 @@
         <v>8.15</v>
       </c>
       <c r="AM13" s="8"/>
+      <c r="AP13" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
@@ -2283,6 +2334,9 @@
         <v>7.99</v>
       </c>
       <c r="AM14" s="8"/>
+      <c r="AP14" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
@@ -2384,6 +2438,9 @@
       <c r="AM15" s="8">
         <v>11.64</v>
       </c>
+      <c r="AP15" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
@@ -2485,6 +2542,9 @@
       <c r="AM16" s="8">
         <v>12.21</v>
       </c>
+      <c r="AP16" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
@@ -2586,6 +2646,9 @@
       <c r="AM17" s="8">
         <v>12.52</v>
       </c>
+      <c r="AP17" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
@@ -2687,6 +2750,9 @@
       <c r="AM18" s="8">
         <v>12.38</v>
       </c>
+      <c r="AP18" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
@@ -2783,6 +2849,9 @@
         <v>8.16</v>
       </c>
       <c r="AM19" s="8"/>
+      <c r="AP19" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
@@ -2879,6 +2948,9 @@
         <v>7.9399999999999995</v>
       </c>
       <c r="AM20" s="8"/>
+      <c r="AP20" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
@@ -2975,6 +3047,9 @@
         <v>7.47</v>
       </c>
       <c r="AM21" s="8"/>
+      <c r="AP21" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
@@ -3982,6 +4057,9 @@
         <v>8.1009999999999991</v>
       </c>
       <c r="AM31" s="8"/>
+      <c r="AP31" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
@@ -4079,6 +4157,9 @@
       </c>
       <c r="AM32" s="8"/>
       <c r="AO32" s="8"/>
+      <c r="AP32" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
@@ -4175,6 +4256,9 @@
         <v>7.5010000000000048</v>
       </c>
       <c r="AM33" s="8"/>
+      <c r="AP33" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
@@ -4370,6 +4454,9 @@
         <v>8.1609999999999978</v>
       </c>
       <c r="AM35" s="8"/>
+      <c r="AP35" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
@@ -4467,6 +4554,9 @@
       </c>
       <c r="AM36" s="8"/>
       <c r="AO36" s="8"/>
+      <c r="AP36" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
@@ -4563,6 +4653,9 @@
         <v>7.5500000000000007</v>
       </c>
       <c r="AM37" s="8"/>
+      <c r="AP37" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
@@ -4763,6 +4856,9 @@
       <c r="AM39" s="8">
         <v>12.469999999999999</v>
       </c>
+      <c r="AP39" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
@@ -4864,6 +4960,9 @@
       <c r="AM40" s="8">
         <v>12.280000000000001</v>
       </c>
+      <c r="AP40" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
@@ -4964,6 +5063,9 @@
       </c>
       <c r="AM41" s="8">
         <v>11.878</v>
+      </c>
+      <c r="AP41" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.3">
@@ -13755,6 +13857,7 @@
     <hyperlink ref="AP89" r:id="rId1" xr:uid="{7F294435-01F3-4E95-B493-E058CDB2E220}"/>
     <hyperlink ref="AP80" r:id="rId2" xr:uid="{CE025F3B-0D0A-4A77-BDB8-5492D21F700D}"/>
     <hyperlink ref="AP54" r:id="rId3" xr:uid="{61E92077-7409-4F39-86D4-8C772F8E125A}"/>
+    <hyperlink ref="AP10" r:id="rId4" xr:uid="{5F449711-4D0D-4141-ABD4-99A8399403D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/video_analysis/WTS_starts.xlsx
+++ b/pages/video_analysis/WTS_starts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E551164-63B0-42FE-8F7D-AB8D9B2E1E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C494BCF-96D8-4104-8A7F-12AED8028121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{BAE2881F-AFDF-458E-BC8D-8FE3C83F19F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="156">
   <si>
     <t>Name</t>
   </si>
@@ -468,6 +468,42 @@
   </si>
   <si>
     <t>https://youtu.be/HtHwScz6RgI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/x-LgPxUgtNQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/xzxBf3ThkVg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4ZBg9qDeFFE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9vMu39HWRAU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/00osXwe25QY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/hegxQC-Etwc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/71w8dLz6m_s</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SOYFmHTm52E</t>
+  </si>
+  <si>
+    <t>https://youtu.be/oMpWPbTRhhw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/BDOhfBoPRGc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/p9Hq3yiwTFg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/q5XkZxT1V1c</t>
   </si>
 </sst>
 </file>
@@ -877,7 +913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6951EBBC-4A15-4CDE-96E1-7BBCD62A6995}">
-  <dimension ref="A1:AP155"/>
+  <dimension ref="A1:AP179"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -887,11 +923,12 @@
     <col min="5" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.21875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="9.21875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="7.33203125" hidden="1" customWidth="1"/>
-    <col min="12" max="16" width="7" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="6.21875" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" customWidth="1"/>
+    <col min="10" max="10" width="9.21875" customWidth="1"/>
+    <col min="11" max="11" width="7.33203125" customWidth="1"/>
+    <col min="12" max="13" width="7" customWidth="1"/>
+    <col min="14" max="16" width="7" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="6.88671875" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="6" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="7" hidden="1" customWidth="1"/>
@@ -13852,6 +13889,1392 @@
         <v>62</v>
       </c>
     </row>
+    <row r="156" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>36</v>
+      </c>
+      <c r="B156" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+      <c r="F156" t="s">
+        <v>51</v>
+      </c>
+      <c r="G156">
+        <v>62.5</v>
+      </c>
+      <c r="J156">
+        <v>27.992000000000001</v>
+      </c>
+      <c r="K156">
+        <v>27.914000000000001</v>
+      </c>
+      <c r="L156">
+        <v>28.052</v>
+      </c>
+      <c r="M156">
+        <v>35.613999999999997</v>
+      </c>
+      <c r="U156">
+        <v>7.7999999999999403E-2</v>
+      </c>
+      <c r="V156">
+        <v>7.6999999999999957</v>
+      </c>
+      <c r="W156" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK156">
+        <v>0.13799999999999812</v>
+      </c>
+      <c r="AL156">
+        <v>7.6219999999999963</v>
+      </c>
+      <c r="AM156" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP156" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="157" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>41</v>
+      </c>
+      <c r="B157" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+      <c r="D157">
+        <v>1</v>
+      </c>
+      <c r="E157">
+        <v>2</v>
+      </c>
+      <c r="F157" t="s">
+        <v>51</v>
+      </c>
+      <c r="G157">
+        <v>62.5</v>
+      </c>
+      <c r="I157">
+        <v>27.492000000000001</v>
+      </c>
+      <c r="J157">
+        <v>27.713999999999999</v>
+      </c>
+      <c r="K157">
+        <v>27.914000000000001</v>
+      </c>
+      <c r="L157">
+        <v>27.855</v>
+      </c>
+      <c r="M157">
+        <v>35.933999999999997</v>
+      </c>
+      <c r="U157">
+        <v>-0.20000000000000284</v>
+      </c>
+      <c r="V157">
+        <v>8.019999999999996</v>
+      </c>
+      <c r="W157" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK157">
+        <v>-5.9000000000001052E-2</v>
+      </c>
+      <c r="AL157">
+        <v>8.2199999999999989</v>
+      </c>
+      <c r="AM157" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP157" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="158" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>38</v>
+      </c>
+      <c r="B158" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>3</v>
+      </c>
+      <c r="F158" t="s">
+        <v>51</v>
+      </c>
+      <c r="G158">
+        <v>62.5</v>
+      </c>
+      <c r="I158">
+        <v>27.513999999999999</v>
+      </c>
+      <c r="J158">
+        <v>27.731999999999999</v>
+      </c>
+      <c r="K158">
+        <v>27.914000000000001</v>
+      </c>
+      <c r="L158">
+        <v>27.914000000000001</v>
+      </c>
+      <c r="M158">
+        <v>36.113999999999997</v>
+      </c>
+      <c r="U158">
+        <v>-0.18200000000000216</v>
+      </c>
+      <c r="V158">
+        <v>8.1999999999999957</v>
+      </c>
+      <c r="W158" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK158">
+        <v>0</v>
+      </c>
+      <c r="AL158">
+        <v>8.3819999999999979</v>
+      </c>
+      <c r="AM158" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP158" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="159" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>40</v>
+      </c>
+      <c r="B159" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159">
+        <v>3</v>
+      </c>
+      <c r="F159" t="s">
+        <v>42</v>
+      </c>
+      <c r="G159">
+        <v>62.5</v>
+      </c>
+      <c r="I159">
+        <v>26.173999999999999</v>
+      </c>
+      <c r="J159">
+        <v>26.434000000000001</v>
+      </c>
+      <c r="K159">
+        <v>26.614999999999998</v>
+      </c>
+      <c r="L159">
+        <v>26.614999999999998</v>
+      </c>
+      <c r="M159">
+        <v>34.673999999999999</v>
+      </c>
+      <c r="U159">
+        <v>-0.18099999999999739</v>
+      </c>
+      <c r="V159">
+        <v>8.0590000000000011</v>
+      </c>
+      <c r="W159" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK159">
+        <v>0</v>
+      </c>
+      <c r="AL159">
+        <v>8.2399999999999984</v>
+      </c>
+      <c r="AM159" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP159" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="160" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>36</v>
+      </c>
+      <c r="B160" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160">
+        <v>2</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+      <c r="F160" t="s">
+        <v>51</v>
+      </c>
+      <c r="G160">
+        <v>62.5</v>
+      </c>
+      <c r="J160">
+        <v>55.014000000000003</v>
+      </c>
+      <c r="K160">
+        <v>54.951999999999998</v>
+      </c>
+      <c r="L160">
+        <v>55.073999999999998</v>
+      </c>
+      <c r="M160">
+        <v>62.613</v>
+      </c>
+      <c r="U160">
+        <v>6.2000000000004718E-2</v>
+      </c>
+      <c r="V160">
+        <v>7.6610000000000014</v>
+      </c>
+      <c r="W160" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK160">
+        <v>0.12199999999999989</v>
+      </c>
+      <c r="AL160">
+        <v>7.5989999999999966</v>
+      </c>
+      <c r="AM160" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP160" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="161" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>41</v>
+      </c>
+      <c r="B161" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161">
+        <v>2</v>
+      </c>
+      <c r="E161">
+        <v>2</v>
+      </c>
+      <c r="F161" t="s">
+        <v>51</v>
+      </c>
+      <c r="G161">
+        <v>62.5</v>
+      </c>
+      <c r="I161">
+        <v>54.451999999999998</v>
+      </c>
+      <c r="J161">
+        <v>54.713999999999999</v>
+      </c>
+      <c r="K161">
+        <v>54.951999999999998</v>
+      </c>
+      <c r="L161">
+        <v>54.914000000000001</v>
+      </c>
+      <c r="M161">
+        <v>62.892000000000003</v>
+      </c>
+      <c r="U161">
+        <v>-0.23799999999999955</v>
+      </c>
+      <c r="V161">
+        <v>7.9400000000000048</v>
+      </c>
+      <c r="W161" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK161">
+        <v>-3.7999999999996703E-2</v>
+      </c>
+      <c r="AL161">
+        <v>8.1780000000000044</v>
+      </c>
+      <c r="AM161" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP161" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="162" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>38</v>
+      </c>
+      <c r="B162" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162">
+        <v>2</v>
+      </c>
+      <c r="E162">
+        <v>3</v>
+      </c>
+      <c r="F162" t="s">
+        <v>51</v>
+      </c>
+      <c r="G162">
+        <v>62.5</v>
+      </c>
+      <c r="I162">
+        <v>54.573999999999998</v>
+      </c>
+      <c r="J162">
+        <v>54.774000000000001</v>
+      </c>
+      <c r="K162">
+        <v>54.951999999999998</v>
+      </c>
+      <c r="L162">
+        <v>54.973999999999997</v>
+      </c>
+      <c r="M162">
+        <v>63.052</v>
+      </c>
+      <c r="U162">
+        <v>-0.17799999999999727</v>
+      </c>
+      <c r="V162">
+        <v>8.1000000000000014</v>
+      </c>
+      <c r="W162" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK162">
+        <v>2.1999999999998465E-2</v>
+      </c>
+      <c r="AL162">
+        <v>8.2779999999999987</v>
+      </c>
+      <c r="AM162" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP162" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="163" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>40</v>
+      </c>
+      <c r="B163" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163">
+        <v>2</v>
+      </c>
+      <c r="E163">
+        <v>3</v>
+      </c>
+      <c r="F163" t="s">
+        <v>42</v>
+      </c>
+      <c r="G163">
+        <v>62.5</v>
+      </c>
+      <c r="I163">
+        <v>52.131</v>
+      </c>
+      <c r="J163">
+        <v>52.332000000000001</v>
+      </c>
+      <c r="K163">
+        <v>52.451999999999998</v>
+      </c>
+      <c r="L163">
+        <v>52.591999999999999</v>
+      </c>
+      <c r="M163">
+        <v>60.572000000000003</v>
+      </c>
+      <c r="U163">
+        <v>-0.11999999999999744</v>
+      </c>
+      <c r="V163">
+        <v>8.1200000000000045</v>
+      </c>
+      <c r="W163" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK163">
+        <v>0.14000000000000057</v>
+      </c>
+      <c r="AL163">
+        <v>8.240000000000002</v>
+      </c>
+      <c r="AM163" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP163" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="164" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>36</v>
+      </c>
+      <c r="B164" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164">
+        <v>3</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+      <c r="F164" t="s">
+        <v>51</v>
+      </c>
+      <c r="G164">
+        <v>125</v>
+      </c>
+      <c r="J164">
+        <v>33.25</v>
+      </c>
+      <c r="K164">
+        <v>33.15</v>
+      </c>
+      <c r="L164">
+        <v>33.311999999999998</v>
+      </c>
+      <c r="M164">
+        <v>40.771999999999998</v>
+      </c>
+      <c r="N164">
+        <v>44.860999999999997</v>
+      </c>
+      <c r="U164">
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="V164">
+        <v>7.6219999999999999</v>
+      </c>
+      <c r="W164">
+        <v>4.0889999999999986</v>
+      </c>
+      <c r="AK164">
+        <v>0.16199999999999903</v>
+      </c>
+      <c r="AL164">
+        <v>7.5219999999999985</v>
+      </c>
+      <c r="AM164">
+        <v>11.610999999999997</v>
+      </c>
+      <c r="AP164" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="165" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>41</v>
+      </c>
+      <c r="B165" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="D165">
+        <v>3</v>
+      </c>
+      <c r="E165">
+        <v>2</v>
+      </c>
+      <c r="F165" t="s">
+        <v>51</v>
+      </c>
+      <c r="G165">
+        <v>125</v>
+      </c>
+      <c r="I165">
+        <v>32.811999999999998</v>
+      </c>
+      <c r="J165">
+        <v>33.052</v>
+      </c>
+      <c r="K165">
+        <v>33.15</v>
+      </c>
+      <c r="L165">
+        <v>33.170999999999999</v>
+      </c>
+      <c r="M165">
+        <v>41.112000000000002</v>
+      </c>
+      <c r="N165">
+        <v>45.19</v>
+      </c>
+      <c r="U165">
+        <v>-9.7999999999998977E-2</v>
+      </c>
+      <c r="V165">
+        <v>7.9620000000000033</v>
+      </c>
+      <c r="W165">
+        <v>4.0779999999999959</v>
+      </c>
+      <c r="AK165">
+        <v>2.1000000000000796E-2</v>
+      </c>
+      <c r="AL165">
+        <v>8.0600000000000023</v>
+      </c>
+      <c r="AM165">
+        <v>12.137999999999998</v>
+      </c>
+      <c r="AP165" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="166" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>38</v>
+      </c>
+      <c r="B166" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166">
+        <v>3</v>
+      </c>
+      <c r="E166">
+        <v>3</v>
+      </c>
+      <c r="F166" t="s">
+        <v>51</v>
+      </c>
+      <c r="G166">
+        <v>125</v>
+      </c>
+      <c r="I166">
+        <v>32.612000000000002</v>
+      </c>
+      <c r="J166">
+        <v>32.97</v>
+      </c>
+      <c r="K166">
+        <v>33.15</v>
+      </c>
+      <c r="L166">
+        <v>33.170999999999999</v>
+      </c>
+      <c r="M166">
+        <v>41.232999999999997</v>
+      </c>
+      <c r="N166">
+        <v>45.350999999999999</v>
+      </c>
+      <c r="U166">
+        <v>-0.17999999999999972</v>
+      </c>
+      <c r="V166">
+        <v>8.0829999999999984</v>
+      </c>
+      <c r="W166">
+        <v>4.1180000000000021</v>
+      </c>
+      <c r="AK166">
+        <v>2.1000000000000796E-2</v>
+      </c>
+      <c r="AL166">
+        <v>8.2629999999999981</v>
+      </c>
+      <c r="AM166">
+        <v>12.381</v>
+      </c>
+      <c r="AP166" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="167" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>40</v>
+      </c>
+      <c r="B167" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167">
+        <v>3</v>
+      </c>
+      <c r="E167">
+        <v>3</v>
+      </c>
+      <c r="F167" t="s">
+        <v>42</v>
+      </c>
+      <c r="G167">
+        <v>125</v>
+      </c>
+      <c r="I167">
+        <v>45.89</v>
+      </c>
+      <c r="J167">
+        <v>46.19</v>
+      </c>
+      <c r="K167">
+        <v>46.271999999999998</v>
+      </c>
+      <c r="L167">
+        <v>46.430999999999997</v>
+      </c>
+      <c r="M167">
+        <v>54.43</v>
+      </c>
+      <c r="N167">
+        <v>58.73</v>
+      </c>
+      <c r="U167">
+        <v>-8.2000000000000739E-2</v>
+      </c>
+      <c r="V167">
+        <v>8.1580000000000013</v>
+      </c>
+      <c r="W167">
+        <v>4.2999999999999972</v>
+      </c>
+      <c r="AK167">
+        <v>0.15899999999999892</v>
+      </c>
+      <c r="AL167">
+        <v>8.240000000000002</v>
+      </c>
+      <c r="AM167">
+        <v>12.54</v>
+      </c>
+      <c r="AP167" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="168" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>36</v>
+      </c>
+      <c r="B168" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C168">
+        <v>2</v>
+      </c>
+      <c r="D168">
+        <v>1</v>
+      </c>
+      <c r="F168" t="s">
+        <v>52</v>
+      </c>
+      <c r="G168">
+        <v>62.5</v>
+      </c>
+      <c r="J168">
+        <v>56.274000000000001</v>
+      </c>
+      <c r="K168">
+        <v>56.194000000000003</v>
+      </c>
+      <c r="L168">
+        <v>56.354999999999997</v>
+      </c>
+      <c r="M168">
+        <v>63.792999999999999</v>
+      </c>
+      <c r="U168">
+        <v>7.9999999999998295E-2</v>
+      </c>
+      <c r="V168">
+        <v>7.5989999999999966</v>
+      </c>
+      <c r="W168" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK168">
+        <v>0.16099999999999426</v>
+      </c>
+      <c r="AL168">
+        <v>7.5189999999999984</v>
+      </c>
+      <c r="AM168" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP168" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="169" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>38</v>
+      </c>
+      <c r="B169" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C169">
+        <v>2</v>
+      </c>
+      <c r="D169">
+        <v>1</v>
+      </c>
+      <c r="F169" t="s">
+        <v>52</v>
+      </c>
+      <c r="G169">
+        <v>62.5</v>
+      </c>
+      <c r="I169">
+        <v>55.792999999999999</v>
+      </c>
+      <c r="J169">
+        <v>56.055</v>
+      </c>
+      <c r="K169">
+        <v>56.194000000000003</v>
+      </c>
+      <c r="L169">
+        <v>56.314</v>
+      </c>
+      <c r="M169">
+        <v>64.192999999999998</v>
+      </c>
+      <c r="U169">
+        <v>-0.1390000000000029</v>
+      </c>
+      <c r="V169">
+        <v>7.9989999999999952</v>
+      </c>
+      <c r="W169" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK169">
+        <v>0.11999999999999744</v>
+      </c>
+      <c r="AL169">
+        <v>8.1379999999999981</v>
+      </c>
+      <c r="AM169" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP169" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="170" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>40</v>
+      </c>
+      <c r="B170" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C170">
+        <v>2</v>
+      </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="F170" t="s">
+        <v>52</v>
+      </c>
+      <c r="G170">
+        <v>62.5</v>
+      </c>
+      <c r="I170">
+        <v>55.732999999999997</v>
+      </c>
+      <c r="J170">
+        <v>56.113999999999997</v>
+      </c>
+      <c r="K170">
+        <v>56.194000000000003</v>
+      </c>
+      <c r="L170">
+        <v>56.334000000000003</v>
+      </c>
+      <c r="M170">
+        <v>64.373000000000005</v>
+      </c>
+      <c r="U170">
+        <v>-8.00000000000054E-2</v>
+      </c>
+      <c r="V170">
+        <v>8.179000000000002</v>
+      </c>
+      <c r="W170" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK170">
+        <v>0.14000000000000057</v>
+      </c>
+      <c r="AL170">
+        <v>8.2590000000000074</v>
+      </c>
+      <c r="AM170" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP170" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="171" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>41</v>
+      </c>
+      <c r="B171" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C171">
+        <v>2</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="F171" t="s">
+        <v>42</v>
+      </c>
+      <c r="G171">
+        <v>62.5</v>
+      </c>
+      <c r="I171">
+        <v>52.334000000000003</v>
+      </c>
+      <c r="J171">
+        <v>52.615000000000002</v>
+      </c>
+      <c r="K171">
+        <v>52.715000000000003</v>
+      </c>
+      <c r="L171">
+        <v>52.773000000000003</v>
+      </c>
+      <c r="M171">
+        <v>60.715000000000003</v>
+      </c>
+      <c r="U171">
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="V171">
+        <v>8</v>
+      </c>
+      <c r="W171" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK171">
+        <v>5.7999999999999829E-2</v>
+      </c>
+      <c r="AL171">
+        <v>8.1000000000000014</v>
+      </c>
+      <c r="AM171" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP171" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="172" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>36</v>
+      </c>
+      <c r="B172" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C172">
+        <v>2</v>
+      </c>
+      <c r="D172">
+        <v>2</v>
+      </c>
+      <c r="F172" t="s">
+        <v>52</v>
+      </c>
+      <c r="G172">
+        <v>62.5</v>
+      </c>
+      <c r="J172">
+        <v>8.7949999999999999</v>
+      </c>
+      <c r="K172">
+        <v>8.7349999999999994</v>
+      </c>
+      <c r="L172">
+        <v>8.8960000000000008</v>
+      </c>
+      <c r="M172">
+        <v>16.376999999999999</v>
+      </c>
+      <c r="U172">
+        <v>6.0000000000000497E-2</v>
+      </c>
+      <c r="V172">
+        <v>7.6419999999999995</v>
+      </c>
+      <c r="W172" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK172">
+        <v>0.16100000000000136</v>
+      </c>
+      <c r="AL172">
+        <v>7.581999999999999</v>
+      </c>
+      <c r="AM172" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP172" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="173" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>38</v>
+      </c>
+      <c r="B173" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C173">
+        <v>2</v>
+      </c>
+      <c r="D173">
+        <v>2</v>
+      </c>
+      <c r="F173" t="s">
+        <v>52</v>
+      </c>
+      <c r="G173">
+        <v>62.5</v>
+      </c>
+      <c r="I173">
+        <v>8.5350000000000001</v>
+      </c>
+      <c r="J173">
+        <v>8.6959999999999997</v>
+      </c>
+      <c r="K173">
+        <v>8.7349999999999994</v>
+      </c>
+      <c r="L173">
+        <v>8.8960000000000008</v>
+      </c>
+      <c r="M173">
+        <v>16.856000000000002</v>
+      </c>
+      <c r="U173">
+        <v>-3.8999999999999702E-2</v>
+      </c>
+      <c r="V173">
+        <v>8.1210000000000022</v>
+      </c>
+      <c r="W173" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK173">
+        <v>0.16100000000000136</v>
+      </c>
+      <c r="AL173">
+        <v>8.1600000000000019</v>
+      </c>
+      <c r="AM173" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP173" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="174" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>40</v>
+      </c>
+      <c r="B174" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C174">
+        <v>2</v>
+      </c>
+      <c r="D174">
+        <v>2</v>
+      </c>
+      <c r="F174" t="s">
+        <v>52</v>
+      </c>
+      <c r="G174">
+        <v>62.5</v>
+      </c>
+      <c r="I174">
+        <v>8.3170000000000002</v>
+      </c>
+      <c r="J174">
+        <v>8.6780000000000008</v>
+      </c>
+      <c r="K174">
+        <v>8.7349999999999994</v>
+      </c>
+      <c r="L174">
+        <v>8.9169999999999998</v>
+      </c>
+      <c r="M174">
+        <v>17.018000000000001</v>
+      </c>
+      <c r="U174">
+        <v>-5.6999999999998607E-2</v>
+      </c>
+      <c r="V174">
+        <v>8.2830000000000013</v>
+      </c>
+      <c r="W174" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK174">
+        <v>0.18200000000000038</v>
+      </c>
+      <c r="AL174">
+        <v>8.34</v>
+      </c>
+      <c r="AM174" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP174" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="175" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>41</v>
+      </c>
+      <c r="B175" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C175">
+        <v>2</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+      <c r="F175" t="s">
+        <v>42</v>
+      </c>
+      <c r="G175">
+        <v>62.5</v>
+      </c>
+      <c r="I175">
+        <v>11.518000000000001</v>
+      </c>
+      <c r="J175">
+        <v>11.818</v>
+      </c>
+      <c r="K175">
+        <v>11.936999999999999</v>
+      </c>
+      <c r="L175">
+        <v>11.936999999999999</v>
+      </c>
+      <c r="M175">
+        <v>19.878</v>
+      </c>
+      <c r="U175">
+        <v>-0.11899999999999977</v>
+      </c>
+      <c r="V175">
+        <v>7.9410000000000007</v>
+      </c>
+      <c r="W175" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK175">
+        <v>0</v>
+      </c>
+      <c r="AL175">
+        <v>8.06</v>
+      </c>
+      <c r="AM175" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP175" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="176" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>36</v>
+      </c>
+      <c r="B176" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C176">
+        <v>2</v>
+      </c>
+      <c r="D176">
+        <v>3</v>
+      </c>
+      <c r="F176" t="s">
+        <v>52</v>
+      </c>
+      <c r="G176">
+        <v>125</v>
+      </c>
+      <c r="J176">
+        <v>8.9610000000000003</v>
+      </c>
+      <c r="K176">
+        <v>8.8610000000000007</v>
+      </c>
+      <c r="L176">
+        <v>9.0410000000000004</v>
+      </c>
+      <c r="M176">
+        <v>16.498999999999999</v>
+      </c>
+      <c r="N176">
+        <v>20.582000000000001</v>
+      </c>
+      <c r="U176">
+        <v>9.9999999999999645E-2</v>
+      </c>
+      <c r="V176">
+        <v>7.6379999999999981</v>
+      </c>
+      <c r="W176">
+        <v>4.083000000000002</v>
+      </c>
+      <c r="AK176">
+        <v>0.17999999999999972</v>
+      </c>
+      <c r="AL176">
+        <v>7.5379999999999985</v>
+      </c>
+      <c r="AM176">
+        <v>11.621</v>
+      </c>
+      <c r="AP176" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="177" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>38</v>
+      </c>
+      <c r="B177" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C177">
+        <v>2</v>
+      </c>
+      <c r="D177">
+        <v>3</v>
+      </c>
+      <c r="F177" t="s">
+        <v>52</v>
+      </c>
+      <c r="G177">
+        <v>125</v>
+      </c>
+      <c r="I177">
+        <v>8.6210000000000004</v>
+      </c>
+      <c r="J177">
+        <v>8.8010000000000002</v>
+      </c>
+      <c r="K177">
+        <v>8.8610000000000007</v>
+      </c>
+      <c r="L177">
+        <v>9.0009999999999994</v>
+      </c>
+      <c r="M177">
+        <v>16.800999999999998</v>
+      </c>
+      <c r="N177">
+        <v>20.940999999999999</v>
+      </c>
+      <c r="U177">
+        <v>-6.0000000000000497E-2</v>
+      </c>
+      <c r="V177">
+        <v>7.9399999999999977</v>
+      </c>
+      <c r="W177">
+        <v>4.1400000000000006</v>
+      </c>
+      <c r="AK177">
+        <v>0.13999999999999879</v>
+      </c>
+      <c r="AL177">
+        <v>7.9999999999999982</v>
+      </c>
+      <c r="AM177">
+        <v>12.139999999999999</v>
+      </c>
+      <c r="AP177" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="178" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>40</v>
+      </c>
+      <c r="B178" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C178">
+        <v>2</v>
+      </c>
+      <c r="D178">
+        <v>3</v>
+      </c>
+      <c r="F178" t="s">
+        <v>52</v>
+      </c>
+      <c r="G178">
+        <v>125</v>
+      </c>
+      <c r="I178">
+        <v>8.4209999999999994</v>
+      </c>
+      <c r="J178">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="K178">
+        <v>8.8610000000000007</v>
+      </c>
+      <c r="L178">
+        <v>8.98</v>
+      </c>
+      <c r="M178">
+        <v>17</v>
+      </c>
+      <c r="N178">
+        <v>21.120999999999999</v>
+      </c>
+      <c r="U178">
+        <v>-8.1000000000001293E-2</v>
+      </c>
+      <c r="V178">
+        <v>8.1389999999999993</v>
+      </c>
+      <c r="W178">
+        <v>4.1209999999999987</v>
+      </c>
+      <c r="AK178">
+        <v>0.11899999999999977</v>
+      </c>
+      <c r="AL178">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="AM178">
+        <v>12.340999999999999</v>
+      </c>
+      <c r="AP178" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="179" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>41</v>
+      </c>
+      <c r="B179" s="6">
+        <v>45110</v>
+      </c>
+      <c r="C179">
+        <v>2</v>
+      </c>
+      <c r="D179">
+        <v>3</v>
+      </c>
+      <c r="F179" t="s">
+        <v>42</v>
+      </c>
+      <c r="G179">
+        <v>62.5</v>
+      </c>
+      <c r="I179">
+        <v>37.802</v>
+      </c>
+      <c r="J179">
+        <v>38.023000000000003</v>
+      </c>
+      <c r="K179">
+        <v>38.081000000000003</v>
+      </c>
+      <c r="L179">
+        <v>38.222999999999999</v>
+      </c>
+      <c r="M179">
+        <v>46.061999999999998</v>
+      </c>
+      <c r="N179">
+        <v>50.281999999999996</v>
+      </c>
+      <c r="U179">
+        <v>-5.7999999999999829E-2</v>
+      </c>
+      <c r="V179">
+        <v>7.9809999999999945</v>
+      </c>
+      <c r="W179">
+        <v>4.2199999999999989</v>
+      </c>
+      <c r="AK179">
+        <v>0.14199999999999591</v>
+      </c>
+      <c r="AL179">
+        <v>8.0389999999999944</v>
+      </c>
+      <c r="AM179">
+        <v>12.258999999999993</v>
+      </c>
+      <c r="AP179" t="s">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="AP89" r:id="rId1" xr:uid="{7F294435-01F3-4E95-B493-E058CDB2E220}"/>

--- a/pages/video_analysis/WTS_starts.xlsx
+++ b/pages/video_analysis/WTS_starts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C494BCF-96D8-4104-8A7F-12AED8028121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB45CF4-8595-4683-B6CD-1DD5F5FDAD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{BAE2881F-AFDF-458E-BC8D-8FE3C83F19F9}"/>
   </bookViews>
@@ -927,24 +927,23 @@
     <col min="9" max="9" width="7.6640625" customWidth="1"/>
     <col min="10" max="10" width="9.21875" customWidth="1"/>
     <col min="11" max="11" width="7.33203125" customWidth="1"/>
-    <col min="12" max="13" width="7" customWidth="1"/>
-    <col min="14" max="16" width="7" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="6.88671875" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="6" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="7" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="6" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="5.21875" hidden="1" customWidth="1"/>
-    <col min="22" max="29" width="4.6640625" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="5.5546875" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="6" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="5" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="6" hidden="1" customWidth="1"/>
-    <col min="34" max="35" width="7" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="6" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="5.5546875" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="8.44140625" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="40" max="41" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="12" max="16" width="7" customWidth="1"/>
+    <col min="17" max="17" width="6.88671875" customWidth="1"/>
+    <col min="18" max="18" width="6" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="6" customWidth="1"/>
+    <col min="21" max="21" width="5.21875" customWidth="1"/>
+    <col min="22" max="29" width="4.6640625" customWidth="1"/>
+    <col min="30" max="30" width="5.5546875" customWidth="1"/>
+    <col min="31" max="31" width="6" customWidth="1"/>
+    <col min="32" max="32" width="5" customWidth="1"/>
+    <col min="33" max="33" width="6" customWidth="1"/>
+    <col min="34" max="35" width="7" customWidth="1"/>
+    <col min="36" max="36" width="6" customWidth="1"/>
+    <col min="37" max="37" width="5.5546875" customWidth="1"/>
+    <col min="38" max="38" width="8.44140625" customWidth="1"/>
+    <col min="39" max="39" width="8.33203125" customWidth="1"/>
+    <col min="40" max="41" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
